--- a/SBM-corps-FHIR/ig/StructureDefinition-fr-service-request-demande-d-examen-ou-de-suivi.xlsx
+++ b/SBM-corps-FHIR/ig/StructureDefinition-fr-service-request-demande-d-examen-ou-de-suivi.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$79</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1993" uniqueCount="474">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2941" uniqueCount="550">
   <si>
     <t>Property</t>
   </si>
@@ -45,7 +45,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>ServiceRequest - Fr Sevice Request Demande d'examen ou de Suivi</t>
+    <t>ServiceRequest - Fr Demande d'examen ou de Suivi</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-25T15:49:50+00:00</t>
+    <t>2025-09-03T12:41:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -830,7 +830,7 @@
 </t>
   </si>
   <si>
-    <t>What is being requested/ordered</t>
+    <t>Type de la demande</t>
   </si>
   <si>
     <t>A code that identifies a particular service (i.e., procedure, diagnostic investigation, or panel of investigations) that have been requested.</t>
@@ -1165,32 +1165,268 @@
 orderer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-practitionerRole-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-practitioner-document)
+    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|Patient|RelatedPerson|Device)
 </t>
   </si>
   <si>
+    <t>Who/what is requesting service</t>
+  </si>
+  <si>
+    <t>The individual who initiated the request and has responsibility for its activation.</t>
+  </si>
+  <si>
+    <t>This not the dispatcher, but rather who is the authorizer.  This element is not intended to handle delegation which would generally be managed through the Provenance resource.</t>
+  </si>
+  <si>
+    <t>Request.requester</t>
+  </si>
+  <si>
+    <t>ORC.12, PRT</t>
+  </si>
+  <si>
+    <t>.participation[typeCode=AUT].role</t>
+  </si>
+  <si>
+    <t>FiveWs.author</t>
+  </si>
+  <si>
+    <t>ClinicalStatement.statementAuthor</t>
+  </si>
+  <si>
+    <t>ServiceRequest.requester.id</t>
+  </si>
+  <si>
+    <t>ServiceRequest.requester.extension</t>
+  </si>
+  <si>
+    <t>ServiceRequest.requester.extension:author</t>
+  </si>
+  <si>
+    <t>author</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-actor-extension}
+</t>
+  </si>
+  <si>
     <t>Auteur de la demande</t>
   </si>
   <si>
-    <t>The individual who initiated the request and has responsibility for its activation.</t>
-  </si>
-  <si>
-    <t>This not the dispatcher, but rather who is the authorizer.  This element is not intended to handle delegation which would generally be managed through the Provenance resource.</t>
-  </si>
-  <si>
-    <t>Request.requester</t>
-  </si>
-  <si>
-    <t>ORC.12, PRT</t>
-  </si>
-  <si>
-    <t>.participation[typeCode=AUT].role</t>
-  </si>
-  <si>
-    <t>FiveWs.author</t>
-  </si>
-  <si>
-    <t>ClinicalStatement.statementAuthor</t>
+    <t>Extension pour représenter un acteur impliqué dans le document avec son type et sa référence.</t>
+  </si>
+  <si>
+    <t>ServiceRequest.requester.extension:author.id</t>
+  </si>
+  <si>
+    <t>ServiceRequest.requester.extension.id</t>
+  </si>
+  <si>
+    <t>ServiceRequest.requester.extension:author.extension</t>
+  </si>
+  <si>
+    <t>ServiceRequest.requester.extension.extension</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>ServiceRequest.requester.extension:author.extension:type</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>ServiceRequest.requester.extension:author.extension:type.id</t>
+  </si>
+  <si>
+    <t>ServiceRequest.requester.extension.extension.id</t>
+  </si>
+  <si>
+    <t>ServiceRequest.requester.extension:author.extension:type.extension</t>
+  </si>
+  <si>
+    <t>ServiceRequest.requester.extension.extension.extension</t>
+  </si>
+  <si>
+    <t>ServiceRequest.requester.extension:author.extension:type.url</t>
+  </si>
+  <si>
+    <t>ServiceRequest.requester.extension.extension.url</t>
+  </si>
+  <si>
+    <t>identifies the meaning of the extension</t>
+  </si>
+  <si>
+    <t>Source of the definition for the extension code - a logical name or a URL.</t>
+  </si>
+  <si>
+    <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
+  </si>
+  <si>
+    <t>Extension.url</t>
+  </si>
+  <si>
+    <t>ServiceRequest.requester.extension:author.extension:type.value[x]</t>
+  </si>
+  <si>
+    <t>ServiceRequest.requester.extension.extension.value[x]</t>
+  </si>
+  <si>
+    <t>Value of extension</t>
+  </si>
+  <si>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
+  </si>
+  <si>
+    <t>AUT</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/document/core/ValueSet/fr-actor-type</t>
+  </si>
+  <si>
+    <t>Extension.value[x]</t>
+  </si>
+  <si>
+    <t>ServiceRequest.requester.extension:author.extension:typeCode</t>
+  </si>
+  <si>
+    <t>typeCode</t>
+  </si>
+  <si>
+    <t>Type de participation</t>
+  </si>
+  <si>
+    <t>ServiceRequest.requester.extension:author.extension:typeCode.id</t>
+  </si>
+  <si>
+    <t>ServiceRequest.requester.extension:author.extension:typeCode.extension</t>
+  </si>
+  <si>
+    <t>ServiceRequest.requester.extension:author.extension:typeCode.url</t>
+  </si>
+  <si>
+    <t>ServiceRequest.requester.extension:author.extension:typeCode.value[x]</t>
+  </si>
+  <si>
+    <t>ServiceRequest.requester.extension:author.extension:reference</t>
+  </si>
+  <si>
+    <t>reference</t>
+  </si>
+  <si>
+    <t>Référence vers le rôle du praticien dans le document</t>
+  </si>
+  <si>
+    <t>ServiceRequest.requester.extension:author.extension:reference.id</t>
+  </si>
+  <si>
+    <t>ServiceRequest.requester.extension:author.extension:reference.extension</t>
+  </si>
+  <si>
+    <t>ServiceRequest.requester.extension:author.extension:reference.url</t>
+  </si>
+  <si>
+    <t>ServiceRequest.requester.extension:author.extension:reference.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-practitionerRole-document|Device|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-device-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-organization-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-related-person-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-patient-ins-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-patient-document)
+</t>
+  </si>
+  <si>
+    <t>ServiceRequest.requester.extension:author.url</t>
+  </si>
+  <si>
+    <t>ServiceRequest.requester.extension.url</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-actor-extension</t>
+  </si>
+  <si>
+    <t>ServiceRequest.requester.extension:author.value[x]</t>
+  </si>
+  <si>
+    <t>ServiceRequest.requester.extension.value[x]</t>
+  </si>
+  <si>
+    <t>base64Binary
+booleancanonicalcodedatedateTimedecimalidinstantintegermarkdownoidpositiveIntstringtimeunsignedInturiurluuidAddressAgeAnnotationAttachmentCodeableConceptCodingContactPointCountDistanceDurationHumanNameIdentifierMoneyPeriodQuantityRangeRatioReferenceSampledDataSignatureTimingContactDetailContributorDataRequirementExpressionParameterDefinitionRelatedArtifactTriggerDefinitionUsageContextDosageMeta</t>
+  </si>
+  <si>
+    <t>ServiceRequest.requester.reference</t>
+  </si>
+  <si>
+    <t>Literal reference, Relative, internal or absolute URL</t>
+  </si>
+  <si>
+    <t>A reference to a location at which the other resource is found. The reference may be a relative reference, in which case it is relative to the service base URL, or an absolute URL that resolves to the location where the resource is found. The reference may be version specific or not. If the reference is not to a FHIR RESTful server, then it should be assumed to be version specific. Internal fragment references (start with '#') refer to contained resources.</t>
+  </si>
+  <si>
+    <t>Using absolute URLs provides a stable scalable approach suitable for a cloud/web context, while using relative/logical references provides a flexible approach suitable for use when trading across closed eco-system boundaries.   Absolute URLs do not need to point to a FHIR RESTful server, though this is the preferred approach. If the URL conforms to the structure "/[type]/[id]" then it should be assumed that the reference is to a FHIR RESTful server.</t>
+  </si>
+  <si>
+    <t>Reference.reference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ref-1
+</t>
+  </si>
+  <si>
+    <t>ServiceRequest.requester.type</t>
+  </si>
+  <si>
+    <t>Type the reference refers to (e.g. "Patient")</t>
+  </si>
+  <si>
+    <t>The expected type of the target of the reference. If both Reference.type and Reference.reference are populated and Reference.reference is a FHIR URL, both SHALL be consistent.
+The type is the Canonical URL of Resource Definition that is the type this reference refers to. References are URLs that are relative to http://hl7.org/fhir/StructureDefinition/ e.g. "Patient" is a reference to http://hl7.org/fhir/StructureDefinition/Patient. Absolute URLs are only allowed for logical models (and can only be used in references in logical models, not resources).</t>
+  </si>
+  <si>
+    <t>This element is used to indicate the type of  the target of the reference. This may be used which ever of the other elements are populated (or not). In some cases, the type of the target may be determined by inspection of the reference (e.g. a RESTful URL) or by resolving the target of the reference; if both the type and a reference is provided, the reference SHALL resolve to a resource of the same type as that specified.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>Aa resource (or, for logical models, the URI of the logical model).</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/resource-types</t>
+  </si>
+  <si>
+    <t>Reference.type</t>
+  </si>
+  <si>
+    <t>ServiceRequest.requester.identifier</t>
+  </si>
+  <si>
+    <t>Logical reference, when literal reference is not known</t>
+  </si>
+  <si>
+    <t>An identifier for the target resource. This is used when there is no way to reference the other resource directly, either because the entity it represents is not available through a FHIR server, or because there is no way for the author of the resource to convert a known identifier to an actual location. There is no requirement that a Reference.identifier point to something that is actually exposed as a FHIR instance, but it SHALL point to a business concept that would be expected to be exposed as a FHIR instance, and that instance would need to be of a FHIR resource type allowed by the reference.</t>
+  </si>
+  <si>
+    <t>When an identifier is provided in place of a reference, any system processing the reference will only be able to resolve the identifier to a reference if it understands the business context in which the identifier is used. Sometimes this is global (e.g. a national identifier) but often it is not. For this reason, none of the useful mechanisms described for working with references (e.g. chaining, includes) are possible, nor should servers be expected to be able resolve the reference. Servers may accept an identifier based reference untouched, resolve it, and/or reject it - see CapabilityStatement.rest.resource.referencePolicy. 
+When both an identifier and a literal reference are provided, the literal reference is preferred. Applications processing the resource are allowed - but not required - to check that the identifier matches the literal reference
+Applications converting a logical reference to a literal reference may choose to leave the logical reference present, or remove it.
+Reference is intended to point to a structure that can potentially be expressed as a FHIR resource, though there is no need for it to exist as an actual FHIR resource instance - except in as much as an application wishes to actual find the target of the reference. The content referred to be the identifier must meet the logical constraints implied by any limitations on what resource types are permitted for the reference.  For example, it would not be legitimate to send the identifier for a drug prescription if the type were Reference(Observation|DiagnosticReport).  One of the use-cases for Reference.identifier is the situation where no FHIR representation exists (where the type is Reference (Any).</t>
+  </si>
+  <si>
+    <t>Reference.identifier</t>
+  </si>
+  <si>
+    <t>ServiceRequest.requester.display</t>
+  </si>
+  <si>
+    <t>Text alternative for the resource</t>
+  </si>
+  <si>
+    <t>Plain text narrative that identifies the resource in addition to the resource reference.</t>
+  </si>
+  <si>
+    <t>This is generally not the same as the Resource.text of the referenced resource.  The purpose is to identify what's being referenced, not to fully describe it.</t>
+  </si>
+  <si>
+    <t>Reference.display</t>
   </si>
   <si>
     <t>ServiceRequest.performerType</t>
@@ -1815,11 +2051,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO53"/>
+  <dimension ref="A1:AO79"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="32.7421875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="30.69921875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="59.6640625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="45.8515625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="11.7578125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="37.7265625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -1828,7 +2064,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="160.10546875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -6547,7 +6783,7 @@
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>377</v>
+        <v>81</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -6563,20 +6799,18 @@
         <v>81</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>229</v>
+        <v>271</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>378</v>
+        <v>272</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>380</v>
-      </c>
+        <v>273</v>
+      </c>
+      <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>81</v>
@@ -6601,13 +6835,13 @@
         <v>81</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>234</v>
+        <v>81</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>381</v>
+        <v>81</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>382</v>
+        <v>81</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>81</v>
@@ -6625,7 +6859,7 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>376</v>
+        <v>274</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -6637,19 +6871,19 @@
         <v>81</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>383</v>
+        <v>81</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>384</v>
+        <v>81</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>385</v>
+        <v>275</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>386</v>
+        <v>81</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>81</v>
@@ -6657,14 +6891,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>388</v>
+        <v>154</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6680,19 +6914,19 @@
         <v>81</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>389</v>
+        <v>135</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>390</v>
+        <v>277</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>391</v>
+        <v>278</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>392</v>
+        <v>157</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6730,19 +6964,19 @@
         <v>81</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>81</v>
+        <v>138</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>81</v>
+        <v>279</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>387</v>
+        <v>280</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -6754,19 +6988,19 @@
         <v>81</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>393</v>
+        <v>81</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>394</v>
+        <v>81</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>395</v>
+        <v>275</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>386</v>
+        <v>81</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>81</v>
@@ -6774,12 +7008,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>396</v>
+        <v>378</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="C43" s="2"/>
+        <v>377</v>
+      </c>
+      <c r="C43" t="s" s="2">
+        <v>379</v>
+      </c>
       <c r="D43" t="s" s="2">
         <v>81</v>
       </c>
@@ -6788,7 +7024,7 @@
         <v>79</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>81</v>
@@ -6797,16 +7033,16 @@
         <v>81</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>229</v>
+        <v>380</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>397</v>
+        <v>381</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>398</v>
+        <v>382</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6833,13 +7069,13 @@
         <v>81</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>234</v>
+        <v>81</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>399</v>
+        <v>81</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>400</v>
+        <v>81</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>81</v>
@@ -6857,7 +7093,7 @@
         <v>81</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>396</v>
+        <v>280</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -6869,7 +7105,7 @@
         <v>81</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>81</v>
@@ -6878,10 +7114,10 @@
         <v>81</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>401</v>
+        <v>81</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>386</v>
+        <v>81</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>81</v>
@@ -6889,10 +7125,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>402</v>
+        <v>383</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>402</v>
+        <v>384</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6903,7 +7139,7 @@
         <v>79</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>81</v>
@@ -6912,16 +7148,16 @@
         <v>81</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>403</v>
+        <v>271</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>397</v>
+        <v>272</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>404</v>
+        <v>273</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6972,19 +7208,19 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>402</v>
+        <v>274</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>81</v>
@@ -6993,10 +7229,10 @@
         <v>81</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>405</v>
+        <v>275</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>386</v>
+        <v>81</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>81</v>
@@ -7004,10 +7240,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>406</v>
+        <v>385</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>406</v>
+        <v>386</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7015,7 +7251,7 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>79</v>
+        <v>387</v>
       </c>
       <c r="G45" t="s" s="2">
         <v>80</v>
@@ -7027,20 +7263,18 @@
         <v>81</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>229</v>
+        <v>135</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>407</v>
+        <v>136</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>409</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>81</v>
@@ -7065,31 +7299,31 @@
         <v>81</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>234</v>
+        <v>81</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>410</v>
+        <v>81</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>411</v>
+        <v>81</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>81</v>
+        <v>138</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>81</v>
+        <v>279</v>
       </c>
       <c r="AD45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>406</v>
+        <v>280</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -7101,19 +7335,19 @@
         <v>81</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>412</v>
+        <v>81</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>413</v>
+        <v>81</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>414</v>
+        <v>81</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>415</v>
+        <v>81</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>81</v>
@@ -7121,21 +7355,23 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>416</v>
+        <v>388</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="C46" s="2"/>
+        <v>386</v>
+      </c>
+      <c r="C46" t="s" s="2">
+        <v>389</v>
+      </c>
       <c r="D46" t="s" s="2">
         <v>81</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>81</v>
@@ -7144,20 +7380,18 @@
         <v>81</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>417</v>
+        <v>135</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>418</v>
+        <v>136</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>420</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>81</v>
@@ -7206,7 +7440,7 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>416</v>
+        <v>280</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -7218,19 +7452,19 @@
         <v>81</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>421</v>
+        <v>81</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>422</v>
+        <v>81</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>423</v>
+        <v>81</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>415</v>
+        <v>81</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>81</v>
@@ -7238,10 +7472,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>424</v>
+        <v>390</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>424</v>
+        <v>391</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7252,7 +7486,7 @@
         <v>79</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>81</v>
@@ -7264,13 +7498,13 @@
         <v>81</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>425</v>
+        <v>271</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>426</v>
+        <v>272</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>427</v>
+        <v>273</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7321,28 +7555,28 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>424</v>
+        <v>274</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>428</v>
+        <v>81</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>429</v>
+        <v>81</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>430</v>
+        <v>275</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>81</v>
@@ -7353,21 +7587,21 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>431</v>
+        <v>392</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>431</v>
+        <v>393</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>432</v>
+        <v>81</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>81</v>
@@ -7379,17 +7613,15 @@
         <v>81</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>433</v>
+        <v>135</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>434</v>
+        <v>136</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>436</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="N48" s="2"/>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>81</v>
@@ -7426,19 +7658,19 @@
         <v>81</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>81</v>
+        <v>138</v>
       </c>
       <c r="AC48" t="s" s="2">
-        <v>81</v>
+        <v>279</v>
       </c>
       <c r="AD48" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>431</v>
+        <v>280</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7450,16 +7682,16 @@
         <v>81</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>437</v>
+        <v>81</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>438</v>
+        <v>81</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>439</v>
+        <v>81</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>81</v>
@@ -7470,10 +7702,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>440</v>
+        <v>394</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>440</v>
+        <v>395</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7481,10 +7713,10 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>81</v>
@@ -7493,19 +7725,19 @@
         <v>81</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>441</v>
+        <v>104</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>442</v>
+        <v>396</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>443</v>
+        <v>397</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>444</v>
+        <v>398</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7513,7 +7745,7 @@
       </c>
       <c r="Q49" s="2"/>
       <c r="R49" t="s" s="2">
-        <v>81</v>
+        <v>389</v>
       </c>
       <c r="S49" t="s" s="2">
         <v>81</v>
@@ -7555,28 +7787,28 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>440</v>
+        <v>399</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>445</v>
+        <v>81</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>446</v>
+        <v>133</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>81</v>
@@ -7587,52 +7819,48 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>447</v>
+        <v>400</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>447</v>
+        <v>401</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>448</v>
+        <v>81</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>229</v>
+        <v>110</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>449</v>
+        <v>402</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>452</v>
-      </c>
+        <v>403</v>
+      </c>
+      <c r="N50" s="2"/>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q50" s="2"/>
       <c r="R50" t="s" s="2">
-        <v>81</v>
+        <v>404</v>
       </c>
       <c r="S50" t="s" s="2">
         <v>81</v>
@@ -7650,13 +7878,11 @@
         <v>81</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="Y50" t="s" s="2">
-        <v>453</v>
-      </c>
+        <v>212</v>
+      </c>
+      <c r="Y50" s="2"/>
       <c r="Z50" t="s" s="2">
-        <v>454</v>
+        <v>405</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>81</v>
@@ -7674,13 +7900,13 @@
         <v>81</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>447</v>
+        <v>406</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>81</v>
@@ -7692,26 +7918,28 @@
         <v>81</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>445</v>
+        <v>81</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>455</v>
+        <v>133</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>456</v>
+        <v>81</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>457</v>
+        <v>407</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="C51" s="2"/>
+        <v>386</v>
+      </c>
+      <c r="C51" t="s" s="2">
+        <v>408</v>
+      </c>
       <c r="D51" t="s" s="2">
         <v>81</v>
       </c>
@@ -7720,7 +7948,7 @@
         <v>79</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>81</v>
@@ -7732,13 +7960,13 @@
         <v>81</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>458</v>
+        <v>135</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>50</v>
+        <v>409</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>459</v>
+        <v>137</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7789,7 +8017,7 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>457</v>
+        <v>280</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -7801,30 +8029,30 @@
         <v>81</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>460</v>
+        <v>81</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>306</v>
+        <v>81</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>461</v>
+        <v>81</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>462</v>
+        <v>81</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>463</v>
+        <v>410</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>463</v>
+        <v>391</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7844,16 +8072,16 @@
         <v>81</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K52" t="s" s="2">
         <v>271</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>464</v>
+        <v>272</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>465</v>
+        <v>273</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7904,7 +8132,7 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>463</v>
+        <v>274</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -7916,16 +8144,16 @@
         <v>81</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>306</v>
+        <v>81</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>466</v>
+        <v>275</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>81</v>
@@ -7936,10 +8164,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>467</v>
+        <v>411</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>467</v>
+        <v>393</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7950,7 +8178,7 @@
         <v>79</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>81</v>
@@ -7962,17 +8190,15 @@
         <v>81</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>468</v>
+        <v>135</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>469</v>
+        <v>136</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>471</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="N53" s="2"/>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>81</v>
@@ -8009,19 +8235,19 @@
         <v>81</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>81</v>
+        <v>138</v>
       </c>
       <c r="AC53" t="s" s="2">
-        <v>81</v>
+        <v>279</v>
       </c>
       <c r="AD53" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>467</v>
+        <v>280</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -8033,26 +8259,3050 @@
         <v>81</v>
       </c>
       <c r="AJ53" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO53" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="54" hidden="true">
+      <c r="A54" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="C54" s="2"/>
+      <c r="D54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E54" s="2"/>
+      <c r="F54" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G54" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K54" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="O54" s="2"/>
+      <c r="P54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q54" s="2"/>
+      <c r="R54" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="S54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF54" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="AG54" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH54" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM54" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AN54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO54" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="55" hidden="true">
+      <c r="A55" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="C55" s="2"/>
+      <c r="D55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E55" s="2"/>
+      <c r="F55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G55" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K55" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="N55" s="2"/>
+      <c r="O55" s="2"/>
+      <c r="P55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q55" s="2"/>
+      <c r="R55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF55" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="AG55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH55" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ55" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="AK53" t="s" s="2">
+      <c r="AK55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM55" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AN55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO55" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="56" hidden="true">
+      <c r="A56" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="C56" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="D56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E56" s="2"/>
+      <c r="F56" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G56" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K56" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="M56" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="N56" s="2"/>
+      <c r="O56" s="2"/>
+      <c r="P56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q56" s="2"/>
+      <c r="R56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF56" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="AG56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ56" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO56" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="57" hidden="true">
+      <c r="A57" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="C57" s="2"/>
+      <c r="D57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E57" s="2"/>
+      <c r="F57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G57" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K57" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="N57" s="2"/>
+      <c r="O57" s="2"/>
+      <c r="P57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q57" s="2"/>
+      <c r="R57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF57" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="AG57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH57" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM57" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="AN57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO57" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="58" hidden="true">
+      <c r="A58" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E58" s="2"/>
+      <c r="F58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K58" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="N58" s="2"/>
+      <c r="O58" s="2"/>
+      <c r="P58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q58" s="2"/>
+      <c r="R58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AF58" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="AG58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO58" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="59" hidden="true">
+      <c r="A59" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E59" s="2"/>
+      <c r="F59" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G59" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K59" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="O59" s="2"/>
+      <c r="P59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q59" s="2"/>
+      <c r="R59" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="S59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF59" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="AG59" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH59" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM59" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AN59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO59" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="60" hidden="true">
+      <c r="A60" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E60" s="2"/>
+      <c r="F60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K60" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
+      <c r="P60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q60" s="2"/>
+      <c r="R60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF60" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="AG60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH60" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AN60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO60" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="61" hidden="true">
+      <c r="A61" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="C61" s="2"/>
+      <c r="D61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E61" s="2"/>
+      <c r="F61" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G61" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K61" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="O61" s="2"/>
+      <c r="P61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q61" s="2"/>
+      <c r="R61" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="S61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF61" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AN61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO61" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="62" hidden="true">
+      <c r="A62" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K62" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="N62" s="2"/>
+      <c r="O62" s="2"/>
+      <c r="P62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q62" s="2"/>
+      <c r="R62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF62" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM62" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AN62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO62" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="63" hidden="true">
+      <c r="A63" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K63" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="O63" s="2"/>
+      <c r="P63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q63" s="2"/>
+      <c r="R63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM63" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AN63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO63" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="64" hidden="true">
+      <c r="A64" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K64" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="O64" s="2"/>
+      <c r="P64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q64" s="2"/>
+      <c r="R64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF64" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AN64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO64" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="65" hidden="true">
+      <c r="A65" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="O65" s="2"/>
+      <c r="P65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AN65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO65" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="66" hidden="true">
+      <c r="A66" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K66" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="O66" s="2"/>
+      <c r="P66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q66" s="2"/>
+      <c r="R66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF66" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AN66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO66" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="67" hidden="true">
+      <c r="A67" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="E67" s="2"/>
+      <c r="F67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G67" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J67" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K67" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="O67" s="2"/>
+      <c r="P67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q67" s="2"/>
+      <c r="R67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X67" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF67" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="AG67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK67" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="AN67" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="AO67" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="68" hidden="true">
+      <c r="A68" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="E68" s="2"/>
+      <c r="F68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J68" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K68" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="O68" s="2"/>
+      <c r="P68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q68" s="2"/>
+      <c r="R68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF68" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK68" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="AN68" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="AO68" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="69" hidden="true">
+      <c r="A69" t="s" s="2">
         <v>472</v>
       </c>
-      <c r="AL53" t="s" s="2">
+      <c r="B69" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E69" s="2"/>
+      <c r="F69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J69" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K69" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="N69" s="2"/>
+      <c r="O69" s="2"/>
+      <c r="P69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q69" s="2"/>
+      <c r="R69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X69" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF69" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="AN69" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="AO69" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="70" hidden="true">
+      <c r="A70" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J70" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K70" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="N70" s="2"/>
+      <c r="O70" s="2"/>
+      <c r="P70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q70" s="2"/>
+      <c r="R70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF70" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="AN70" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="AO70" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="71" hidden="true">
+      <c r="A71" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J71" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K71" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="O71" s="2"/>
+      <c r="P71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q71" s="2"/>
+      <c r="R71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF71" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK71" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="AN71" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="AO71" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="72" hidden="true">
+      <c r="A72" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J72" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K72" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="O72" s="2"/>
+      <c r="P72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q72" s="2"/>
+      <c r="R72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF72" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="AG72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ72" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK72" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="AM72" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="AN72" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="AO72" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="73" hidden="true">
+      <c r="A73" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="C73" s="2"/>
+      <c r="D73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E73" s="2"/>
+      <c r="F73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K73" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="N73" s="2"/>
+      <c r="O73" s="2"/>
+      <c r="P73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q73" s="2"/>
+      <c r="R73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF73" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="AG73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK73" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="AM73" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="AN73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO73" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="74" hidden="true">
+      <c r="A74" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="E74" s="2"/>
+      <c r="F74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K74" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="O74" s="2"/>
+      <c r="P74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q74" s="2"/>
+      <c r="R74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF74" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="AG74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK74" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="AN74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO74" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="75" hidden="true">
+      <c r="A75" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="C75" s="2"/>
+      <c r="D75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E75" s="2"/>
+      <c r="F75" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J75" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K75" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="O75" s="2"/>
+      <c r="P75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q75" s="2"/>
+      <c r="R75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF75" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="AG75" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ75" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL75" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="AM75" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="AN75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO75" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="76" hidden="true">
+      <c r="A76" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="C76" s="2"/>
+      <c r="D76" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="E76" s="2"/>
+      <c r="F76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H76" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="I76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J76" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K76" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="L76" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="O76" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="P76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q76" s="2"/>
+      <c r="R76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X76" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="Y76" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="Z76" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF76" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="AG76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ76" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL76" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="AM76" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="AN76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO76" t="s" s="2">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="77" hidden="true">
+      <c r="A77" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="C77" s="2"/>
+      <c r="D77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E77" s="2"/>
+      <c r="F77" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K77" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="L77" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="M77" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="N77" s="2"/>
+      <c r="O77" s="2"/>
+      <c r="P77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q77" s="2"/>
+      <c r="R77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF77" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="AG77" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ77" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK77" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="AL77" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="AM77" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="AN77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO77" t="s" s="2">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="78" hidden="true">
+      <c r="A78" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="C78" s="2"/>
+      <c r="D78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E78" s="2"/>
+      <c r="F78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G78" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J78" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K78" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="L78" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="M78" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="N78" s="2"/>
+      <c r="O78" s="2"/>
+      <c r="P78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q78" s="2"/>
+      <c r="R78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF78" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="AG78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH78" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ78" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL78" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="AM78" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="AN78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO78" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="79" hidden="true">
+      <c r="A79" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="C79" s="2"/>
+      <c r="D79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E79" s="2"/>
+      <c r="F79" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K79" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="L79" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="M79" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="N79" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="O79" s="2"/>
+      <c r="P79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q79" s="2"/>
+      <c r="R79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF79" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="AG79" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ79" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK79" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="AL79" t="s" s="2">
         <v>133</v>
       </c>
-      <c r="AM53" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="AN53" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO53" t="s" s="2">
+      <c r="AM79" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="AN79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO79" t="s" s="2">
         <v>81</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO53">
+  <autoFilter ref="A1:AO79">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -8062,7 +11312,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI52">
+  <conditionalFormatting sqref="A2:AI78">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/SBM-corps-FHIR/ig/StructureDefinition-fr-service-request-demande-d-examen-ou-de-suivi.xlsx
+++ b/SBM-corps-FHIR/ig/StructureDefinition-fr-service-request-demande-d-examen-ou-de-suivi.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-03T12:41:15+00:00</t>
+    <t>2025-09-04T10:23:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
